--- a/data/luat_dat_dai/Luat_dat_dai_file.xlsx
+++ b/data/luat_dat_dai/Luat_dat_dai_file.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\LawAssistant\triplet_extraction\data\luat_dat_dai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\LawAssistant\data\luat_dat_dai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF1F9A8-7E83-498D-AD95-E7FE1E6698D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87819BFC-B3D8-4C6B-97CF-0F5274F5ACCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{75A87B30-D479-4520-B3E8-6EE7229C7E16}"/>
   </bookViews>
@@ -1148,9 +1148,9 @@
     <col min="2" max="2" width="28" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="43.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1166,13 +1166,13 @@
       <c r="D1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>191</v>
       </c>
     </row>
@@ -1189,10 +1189,10 @@
       <c r="D2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       <c r="D3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       <c r="D6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       <c r="D15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="3" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       <c r="D24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="3" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       <c r="D32" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="3" t="s">
         <v>183</v>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       <c r="D37" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="3" t="s">
         <v>181</v>
       </c>
     </row>
@@ -1748,13 +1748,13 @@
       <c r="D40" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="3" t="s">
         <v>190</v>
       </c>
     </row>
@@ -1771,10 +1771,10 @@
       <c r="D41" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="3" t="s">
         <v>186</v>
       </c>
     </row>
